--- a/samples/历史销量导入-含错误.xlsx
+++ b/samples/历史销量导入-含错误.xlsx
@@ -453,7 +453,7 @@
         <v>46269</v>
       </c>
       <c r="C5">
-        <v>12.5</v>
+        <v>1.2345</v>
       </c>
     </row>
     <row r="6">
